--- a/Student Attendance/ECE (ROSE)/ECE (ROSE) Monthly Attendance - October-2024.xlsx
+++ b/Student Attendance/ECE (ROSE)/ECE (ROSE) Monthly Attendance - October-2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Student Attendance\ECE (ROSE)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617DB83B-5B8C-42D0-94E7-DA8EAFE6AE64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF25128-4EE0-4BC9-8490-6513C21751BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -697,14 +697,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="17" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -720,16 +730,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1136,104 +1136,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="33"/>
-      <c r="AI1" s="33"/>
-      <c r="AJ1" s="33"/>
-      <c r="AK1" s="41"/>
-      <c r="AL1" s="41"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="37"/>
+      <c r="AI1" s="37"/>
+      <c r="AJ1" s="37"/>
+      <c r="AK1" s="33"/>
+      <c r="AL1" s="33"/>
     </row>
     <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="34"/>
-      <c r="V2" s="34"/>
-      <c r="W2" s="34"/>
-      <c r="X2" s="34"/>
-      <c r="Y2" s="34"/>
-      <c r="Z2" s="34"/>
-      <c r="AA2" s="34"/>
-      <c r="AB2" s="34"/>
-      <c r="AC2" s="34"/>
-      <c r="AD2" s="34"/>
-      <c r="AE2" s="34"/>
-      <c r="AF2" s="34"/>
-      <c r="AG2" s="34"/>
-      <c r="AH2" s="34"/>
-      <c r="AI2" s="34"/>
-      <c r="AJ2" s="34"/>
-      <c r="AK2" s="40"/>
-      <c r="AL2" s="40"/>
-      <c r="AM2" s="40"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="36"/>
+      <c r="AE2" s="36"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
+      <c r="AJ2" s="36"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="32"/>
+      <c r="AM2" s="32"/>
     </row>
     <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="38" t="s">
+      <c r="A3" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="42" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1360,25 +1360,25 @@
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="AK3" s="32" t="s">
+      <c r="AK3" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="AL3" s="32" t="s">
+      <c r="AL3" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="AM3" s="35" t="s">
+      <c r="AM3" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="AN3" s="36"/>
+      <c r="AN3" s="40"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
     </row>
     <row r="4" spans="1:42" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="39"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
       <c r="F4" s="23">
         <v>45566</v>
       </c>
@@ -1472,8 +1472,8 @@
       <c r="AJ4" s="23">
         <v>45596</v>
       </c>
-      <c r="AK4" s="32"/>
-      <c r="AL4" s="32"/>
+      <c r="AK4" s="35"/>
+      <c r="AL4" s="35"/>
       <c r="AM4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1497,44 +1497,44 @@
       <c r="E5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="43"/>
+      <c r="F5" s="34"/>
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="42" t="s">
+      <c r="K5" s="38" t="s">
         <v>118</v>
       </c>
       <c r="L5" s="12"/>
-      <c r="M5" s="43"/>
+      <c r="M5" s="34"/>
       <c r="N5" s="12"/>
       <c r="O5" s="12"/>
       <c r="P5" s="12"/>
       <c r="Q5" s="12"/>
-      <c r="R5" s="42" t="s">
+      <c r="R5" s="38" t="s">
         <v>118</v>
       </c>
       <c r="S5" s="12"/>
-      <c r="T5" s="43"/>
+      <c r="T5" s="34"/>
       <c r="U5" s="12"/>
       <c r="V5" s="12"/>
       <c r="W5" s="12"/>
       <c r="X5" s="12"/>
-      <c r="Y5" s="42" t="s">
+      <c r="Y5" s="38" t="s">
         <v>118</v>
       </c>
       <c r="Z5" s="12"/>
-      <c r="AA5" s="43"/>
+      <c r="AA5" s="34"/>
       <c r="AB5" s="12"/>
       <c r="AC5" s="12"/>
       <c r="AD5" s="12"/>
       <c r="AE5" s="12"/>
-      <c r="AF5" s="42" t="s">
+      <c r="AF5" s="38" t="s">
         <v>118</v>
       </c>
       <c r="AG5" s="12"/>
       <c r="AH5" s="12"/>
-      <c r="AI5" s="43"/>
+      <c r="AI5" s="34"/>
       <c r="AJ5" s="12"/>
       <c r="AK5" s="5">
         <f t="shared" ref="AK5:AK34" si="2">COUNTIF(F5:AJ5,"P")</f>
@@ -1569,36 +1569,36 @@
       <c r="E6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="43"/>
+      <c r="F6" s="34"/>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
-      <c r="K6" s="42"/>
+      <c r="K6" s="38"/>
       <c r="L6" s="12"/>
-      <c r="M6" s="43"/>
+      <c r="M6" s="34"/>
       <c r="N6" s="12"/>
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
       <c r="Q6" s="12"/>
-      <c r="R6" s="42"/>
+      <c r="R6" s="38"/>
       <c r="S6" s="12"/>
-      <c r="T6" s="43"/>
+      <c r="T6" s="34"/>
       <c r="U6" s="12"/>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
       <c r="X6" s="12"/>
-      <c r="Y6" s="42"/>
+      <c r="Y6" s="38"/>
       <c r="Z6" s="12"/>
-      <c r="AA6" s="43"/>
+      <c r="AA6" s="34"/>
       <c r="AB6" s="12"/>
       <c r="AC6" s="12"/>
       <c r="AD6" s="12"/>
       <c r="AE6" s="12"/>
-      <c r="AF6" s="42"/>
+      <c r="AF6" s="38"/>
       <c r="AG6" s="12"/>
       <c r="AH6" s="12"/>
-      <c r="AI6" s="43"/>
+      <c r="AI6" s="34"/>
       <c r="AJ6" s="12"/>
       <c r="AK6" s="5">
         <f t="shared" si="2"/>
@@ -1631,36 +1631,36 @@
       <c r="E7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="43"/>
+      <c r="F7" s="34"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
       <c r="J7" s="12"/>
-      <c r="K7" s="42"/>
+      <c r="K7" s="38"/>
       <c r="L7" s="12"/>
-      <c r="M7" s="43"/>
+      <c r="M7" s="34"/>
       <c r="N7" s="12"/>
       <c r="O7" s="12"/>
       <c r="P7" s="12"/>
       <c r="Q7" s="12"/>
-      <c r="R7" s="42"/>
+      <c r="R7" s="38"/>
       <c r="S7" s="12"/>
-      <c r="T7" s="43"/>
+      <c r="T7" s="34"/>
       <c r="U7" s="12"/>
       <c r="V7" s="12"/>
       <c r="W7" s="12"/>
       <c r="X7" s="12"/>
-      <c r="Y7" s="42"/>
+      <c r="Y7" s="38"/>
       <c r="Z7" s="12"/>
-      <c r="AA7" s="43"/>
+      <c r="AA7" s="34"/>
       <c r="AB7" s="12"/>
       <c r="AC7" s="12"/>
       <c r="AD7" s="12"/>
       <c r="AE7" s="12"/>
-      <c r="AF7" s="42"/>
+      <c r="AF7" s="38"/>
       <c r="AG7" s="12"/>
       <c r="AH7" s="12"/>
-      <c r="AI7" s="43"/>
+      <c r="AI7" s="34"/>
       <c r="AJ7" s="12"/>
       <c r="AK7" s="5">
         <f t="shared" si="2"/>
@@ -1691,36 +1691,36 @@
       <c r="E8" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="43"/>
+      <c r="F8" s="34"/>
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
-      <c r="K8" s="42"/>
+      <c r="K8" s="38"/>
       <c r="L8" s="12"/>
-      <c r="M8" s="43"/>
+      <c r="M8" s="34"/>
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
       <c r="Q8" s="12"/>
-      <c r="R8" s="42"/>
+      <c r="R8" s="38"/>
       <c r="S8" s="12"/>
-      <c r="T8" s="43"/>
+      <c r="T8" s="34"/>
       <c r="U8" s="12"/>
       <c r="V8" s="12"/>
       <c r="W8" s="12"/>
       <c r="X8" s="12"/>
-      <c r="Y8" s="42"/>
+      <c r="Y8" s="38"/>
       <c r="Z8" s="12"/>
-      <c r="AA8" s="43"/>
+      <c r="AA8" s="34"/>
       <c r="AB8" s="12"/>
       <c r="AC8" s="12"/>
       <c r="AD8" s="12"/>
       <c r="AE8" s="12"/>
-      <c r="AF8" s="42"/>
+      <c r="AF8" s="38"/>
       <c r="AG8" s="12"/>
       <c r="AH8" s="12"/>
-      <c r="AI8" s="43"/>
+      <c r="AI8" s="34"/>
       <c r="AJ8" s="12"/>
       <c r="AK8" s="5">
         <f t="shared" si="2"/>
@@ -1730,12 +1730,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AM8" s="35" t="s">
+      <c r="AM8" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="AN8" s="37"/>
-      <c r="AO8" s="37"/>
-      <c r="AP8" s="36"/>
+      <c r="AN8" s="41"/>
+      <c r="AO8" s="41"/>
+      <c r="AP8" s="40"/>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -1753,36 +1753,36 @@
       <c r="E9" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="43"/>
+      <c r="F9" s="34"/>
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
-      <c r="K9" s="42"/>
+      <c r="K9" s="38"/>
       <c r="L9" s="12"/>
-      <c r="M9" s="43"/>
+      <c r="M9" s="34"/>
       <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
       <c r="Q9" s="12"/>
-      <c r="R9" s="42"/>
+      <c r="R9" s="38"/>
       <c r="S9" s="12"/>
-      <c r="T9" s="43"/>
+      <c r="T9" s="34"/>
       <c r="U9" s="12"/>
       <c r="V9" s="12"/>
       <c r="W9" s="12"/>
       <c r="X9" s="12"/>
-      <c r="Y9" s="42"/>
+      <c r="Y9" s="38"/>
       <c r="Z9" s="12"/>
-      <c r="AA9" s="43"/>
+      <c r="AA9" s="34"/>
       <c r="AB9" s="12"/>
       <c r="AC9" s="12"/>
       <c r="AD9" s="12"/>
       <c r="AE9" s="12"/>
-      <c r="AF9" s="42"/>
+      <c r="AF9" s="38"/>
       <c r="AG9" s="12"/>
       <c r="AH9" s="12"/>
-      <c r="AI9" s="43"/>
+      <c r="AI9" s="34"/>
       <c r="AJ9" s="12"/>
       <c r="AK9" s="5">
         <f t="shared" si="2"/>
@@ -1821,36 +1821,36 @@
       <c r="E10" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="43"/>
+      <c r="F10" s="34"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
-      <c r="K10" s="42"/>
+      <c r="K10" s="38"/>
       <c r="L10" s="12"/>
-      <c r="M10" s="43"/>
+      <c r="M10" s="34"/>
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
       <c r="Q10" s="12"/>
-      <c r="R10" s="42"/>
+      <c r="R10" s="38"/>
       <c r="S10" s="12"/>
-      <c r="T10" s="43"/>
+      <c r="T10" s="34"/>
       <c r="U10" s="12"/>
       <c r="V10" s="12"/>
       <c r="W10" s="12"/>
       <c r="X10" s="12"/>
-      <c r="Y10" s="42"/>
+      <c r="Y10" s="38"/>
       <c r="Z10" s="12"/>
-      <c r="AA10" s="43"/>
+      <c r="AA10" s="34"/>
       <c r="AB10" s="12"/>
       <c r="AC10" s="12"/>
       <c r="AD10" s="12"/>
       <c r="AE10" s="12"/>
-      <c r="AF10" s="42"/>
+      <c r="AF10" s="38"/>
       <c r="AG10" s="12"/>
       <c r="AH10" s="12"/>
-      <c r="AI10" s="43"/>
+      <c r="AI10" s="34"/>
       <c r="AJ10" s="12"/>
       <c r="AK10" s="5">
         <f t="shared" si="2"/>
@@ -1892,36 +1892,36 @@
       <c r="E11" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="43"/>
+      <c r="F11" s="34"/>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
-      <c r="K11" s="42"/>
+      <c r="K11" s="38"/>
       <c r="L11" s="12"/>
-      <c r="M11" s="43"/>
+      <c r="M11" s="34"/>
       <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
       <c r="Q11" s="12"/>
-      <c r="R11" s="42"/>
+      <c r="R11" s="38"/>
       <c r="S11" s="12"/>
-      <c r="T11" s="43"/>
+      <c r="T11" s="34"/>
       <c r="U11" s="12"/>
       <c r="V11" s="12"/>
       <c r="W11" s="12"/>
       <c r="X11" s="12"/>
-      <c r="Y11" s="42"/>
+      <c r="Y11" s="38"/>
       <c r="Z11" s="12"/>
-      <c r="AA11" s="43"/>
+      <c r="AA11" s="34"/>
       <c r="AB11" s="12"/>
       <c r="AC11" s="12"/>
       <c r="AD11" s="12"/>
       <c r="AE11" s="12"/>
-      <c r="AF11" s="42"/>
+      <c r="AF11" s="38"/>
       <c r="AG11" s="12"/>
       <c r="AH11" s="12"/>
-      <c r="AI11" s="43"/>
+      <c r="AI11" s="34"/>
       <c r="AJ11" s="12"/>
       <c r="AK11" s="5">
         <f t="shared" si="2"/>
@@ -1961,36 +1961,36 @@
       <c r="E12" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="43"/>
+      <c r="F12" s="34"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
-      <c r="K12" s="42"/>
+      <c r="K12" s="38"/>
       <c r="L12" s="12"/>
-      <c r="M12" s="43"/>
+      <c r="M12" s="34"/>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
       <c r="Q12" s="12"/>
-      <c r="R12" s="42"/>
+      <c r="R12" s="38"/>
       <c r="S12" s="12"/>
-      <c r="T12" s="43"/>
+      <c r="T12" s="34"/>
       <c r="U12" s="12"/>
       <c r="V12" s="12"/>
       <c r="W12" s="12"/>
       <c r="X12" s="12"/>
-      <c r="Y12" s="42"/>
+      <c r="Y12" s="38"/>
       <c r="Z12" s="12"/>
-      <c r="AA12" s="43"/>
+      <c r="AA12" s="34"/>
       <c r="AB12" s="12"/>
       <c r="AC12" s="12"/>
       <c r="AD12" s="12"/>
       <c r="AE12" s="12"/>
-      <c r="AF12" s="42"/>
+      <c r="AF12" s="38"/>
       <c r="AG12" s="12"/>
       <c r="AH12" s="12"/>
-      <c r="AI12" s="43"/>
+      <c r="AI12" s="34"/>
       <c r="AJ12" s="12"/>
       <c r="AK12" s="5">
         <f t="shared" si="2"/>
@@ -2032,36 +2032,36 @@
       <c r="E13" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="43"/>
+      <c r="F13" s="34"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
-      <c r="K13" s="42"/>
+      <c r="K13" s="38"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="43"/>
+      <c r="M13" s="34"/>
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
-      <c r="R13" s="42"/>
+      <c r="R13" s="38"/>
       <c r="S13" s="12"/>
-      <c r="T13" s="43"/>
+      <c r="T13" s="34"/>
       <c r="U13" s="12"/>
       <c r="V13" s="12"/>
       <c r="W13" s="12"/>
       <c r="X13" s="12"/>
-      <c r="Y13" s="42"/>
+      <c r="Y13" s="38"/>
       <c r="Z13" s="12"/>
-      <c r="AA13" s="43"/>
+      <c r="AA13" s="34"/>
       <c r="AB13" s="12"/>
       <c r="AC13" s="12"/>
       <c r="AD13" s="12"/>
       <c r="AE13" s="12"/>
-      <c r="AF13" s="42"/>
+      <c r="AF13" s="38"/>
       <c r="AG13" s="12"/>
       <c r="AH13" s="12"/>
-      <c r="AI13" s="43"/>
+      <c r="AI13" s="34"/>
       <c r="AJ13" s="12"/>
       <c r="AK13" s="5">
         <f t="shared" si="2"/>
@@ -2092,36 +2092,36 @@
       <c r="E14" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="43"/>
+      <c r="F14" s="34"/>
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="42"/>
+      <c r="K14" s="38"/>
       <c r="L14" s="12"/>
-      <c r="M14" s="43"/>
+      <c r="M14" s="34"/>
       <c r="N14" s="12"/>
       <c r="O14" s="12"/>
       <c r="P14" s="12"/>
       <c r="Q14" s="12"/>
-      <c r="R14" s="42"/>
+      <c r="R14" s="38"/>
       <c r="S14" s="12"/>
-      <c r="T14" s="43"/>
+      <c r="T14" s="34"/>
       <c r="U14" s="12"/>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
       <c r="X14" s="12"/>
-      <c r="Y14" s="42"/>
+      <c r="Y14" s="38"/>
       <c r="Z14" s="12"/>
-      <c r="AA14" s="43"/>
+      <c r="AA14" s="34"/>
       <c r="AB14" s="12"/>
       <c r="AC14" s="12"/>
       <c r="AD14" s="12"/>
       <c r="AE14" s="12"/>
-      <c r="AF14" s="42"/>
+      <c r="AF14" s="38"/>
       <c r="AG14" s="12"/>
       <c r="AH14" s="12"/>
-      <c r="AI14" s="43"/>
+      <c r="AI14" s="34"/>
       <c r="AJ14" s="12"/>
       <c r="AK14" s="5">
         <f t="shared" si="2"/>
@@ -2152,36 +2152,36 @@
       <c r="E15" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="43"/>
+      <c r="F15" s="34"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
-      <c r="K15" s="42"/>
+      <c r="K15" s="38"/>
       <c r="L15" s="12"/>
-      <c r="M15" s="43"/>
+      <c r="M15" s="34"/>
       <c r="N15" s="12"/>
       <c r="O15" s="12"/>
       <c r="P15" s="12"/>
       <c r="Q15" s="12"/>
-      <c r="R15" s="42"/>
+      <c r="R15" s="38"/>
       <c r="S15" s="12"/>
-      <c r="T15" s="43"/>
+      <c r="T15" s="34"/>
       <c r="U15" s="12"/>
       <c r="V15" s="12"/>
       <c r="W15" s="12"/>
       <c r="X15" s="12"/>
-      <c r="Y15" s="42"/>
+      <c r="Y15" s="38"/>
       <c r="Z15" s="12"/>
-      <c r="AA15" s="43"/>
+      <c r="AA15" s="34"/>
       <c r="AB15" s="12"/>
       <c r="AC15" s="12"/>
       <c r="AD15" s="12"/>
       <c r="AE15" s="12"/>
-      <c r="AF15" s="42"/>
+      <c r="AF15" s="38"/>
       <c r="AG15" s="12"/>
       <c r="AH15" s="12"/>
-      <c r="AI15" s="43"/>
+      <c r="AI15" s="34"/>
       <c r="AJ15" s="12"/>
       <c r="AK15" s="5">
         <f t="shared" si="2"/>
@@ -2212,36 +2212,36 @@
       <c r="E16" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="43"/>
+      <c r="F16" s="34"/>
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
-      <c r="K16" s="42"/>
+      <c r="K16" s="38"/>
       <c r="L16" s="12"/>
-      <c r="M16" s="43"/>
+      <c r="M16" s="34"/>
       <c r="N16" s="12"/>
       <c r="O16" s="12"/>
       <c r="P16" s="12"/>
       <c r="Q16" s="12"/>
-      <c r="R16" s="42"/>
+      <c r="R16" s="38"/>
       <c r="S16" s="12"/>
-      <c r="T16" s="43"/>
+      <c r="T16" s="34"/>
       <c r="U16" s="12"/>
       <c r="V16" s="12"/>
       <c r="W16" s="12"/>
       <c r="X16" s="12"/>
-      <c r="Y16" s="42"/>
+      <c r="Y16" s="38"/>
       <c r="Z16" s="12"/>
-      <c r="AA16" s="43"/>
+      <c r="AA16" s="34"/>
       <c r="AB16" s="12"/>
       <c r="AC16" s="12"/>
       <c r="AD16" s="12"/>
       <c r="AE16" s="12"/>
-      <c r="AF16" s="42"/>
+      <c r="AF16" s="38"/>
       <c r="AG16" s="12"/>
       <c r="AH16" s="12"/>
-      <c r="AI16" s="43"/>
+      <c r="AI16" s="34"/>
       <c r="AJ16" s="12"/>
       <c r="AK16" s="5">
         <f t="shared" si="2"/>
@@ -2251,12 +2251,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AM16" s="35" t="s">
+      <c r="AM16" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="AN16" s="37"/>
-      <c r="AO16" s="37"/>
-      <c r="AP16" s="36"/>
+      <c r="AN16" s="41"/>
+      <c r="AO16" s="41"/>
+      <c r="AP16" s="40"/>
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
@@ -2274,36 +2274,36 @@
       <c r="E17" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="43"/>
+      <c r="F17" s="34"/>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
-      <c r="K17" s="42"/>
+      <c r="K17" s="38"/>
       <c r="L17" s="12"/>
-      <c r="M17" s="43"/>
+      <c r="M17" s="34"/>
       <c r="N17" s="12"/>
       <c r="O17" s="12"/>
       <c r="P17" s="12"/>
       <c r="Q17" s="12"/>
-      <c r="R17" s="42"/>
+      <c r="R17" s="38"/>
       <c r="S17" s="12"/>
-      <c r="T17" s="43"/>
+      <c r="T17" s="34"/>
       <c r="U17" s="12"/>
       <c r="V17" s="12"/>
       <c r="W17" s="12"/>
       <c r="X17" s="12"/>
-      <c r="Y17" s="42"/>
+      <c r="Y17" s="38"/>
       <c r="Z17" s="12"/>
-      <c r="AA17" s="43"/>
+      <c r="AA17" s="34"/>
       <c r="AB17" s="12"/>
       <c r="AC17" s="12"/>
       <c r="AD17" s="12"/>
       <c r="AE17" s="12"/>
-      <c r="AF17" s="42"/>
+      <c r="AF17" s="38"/>
       <c r="AG17" s="12"/>
       <c r="AH17" s="12"/>
-      <c r="AI17" s="43"/>
+      <c r="AI17" s="34"/>
       <c r="AJ17" s="12"/>
       <c r="AK17" s="5">
         <f t="shared" si="2"/>
@@ -2342,36 +2342,36 @@
       <c r="E18" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="43"/>
+      <c r="F18" s="34"/>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
-      <c r="K18" s="42"/>
+      <c r="K18" s="38"/>
       <c r="L18" s="12"/>
-      <c r="M18" s="43"/>
+      <c r="M18" s="34"/>
       <c r="N18" s="12"/>
       <c r="O18" s="12"/>
       <c r="P18" s="12"/>
       <c r="Q18" s="12"/>
-      <c r="R18" s="42"/>
+      <c r="R18" s="38"/>
       <c r="S18" s="12"/>
-      <c r="T18" s="43"/>
+      <c r="T18" s="34"/>
       <c r="U18" s="12"/>
       <c r="V18" s="12"/>
       <c r="W18" s="12"/>
       <c r="X18" s="12"/>
-      <c r="Y18" s="42"/>
+      <c r="Y18" s="38"/>
       <c r="Z18" s="12"/>
-      <c r="AA18" s="43"/>
+      <c r="AA18" s="34"/>
       <c r="AB18" s="12"/>
       <c r="AC18" s="12"/>
       <c r="AD18" s="12"/>
       <c r="AE18" s="12"/>
-      <c r="AF18" s="42"/>
+      <c r="AF18" s="38"/>
       <c r="AG18" s="12"/>
       <c r="AH18" s="12"/>
-      <c r="AI18" s="43"/>
+      <c r="AI18" s="34"/>
       <c r="AJ18" s="12"/>
       <c r="AK18" s="5">
         <f t="shared" si="2"/>
@@ -2413,36 +2413,36 @@
       <c r="E19" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="43"/>
+      <c r="F19" s="34"/>
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
-      <c r="K19" s="42"/>
+      <c r="K19" s="38"/>
       <c r="L19" s="12"/>
-      <c r="M19" s="43"/>
+      <c r="M19" s="34"/>
       <c r="N19" s="12"/>
       <c r="O19" s="12"/>
       <c r="P19" s="12"/>
       <c r="Q19" s="12"/>
-      <c r="R19" s="42"/>
+      <c r="R19" s="38"/>
       <c r="S19" s="12"/>
-      <c r="T19" s="43"/>
+      <c r="T19" s="34"/>
       <c r="U19" s="12"/>
       <c r="V19" s="12"/>
       <c r="W19" s="12"/>
       <c r="X19" s="12"/>
-      <c r="Y19" s="42"/>
+      <c r="Y19" s="38"/>
       <c r="Z19" s="12"/>
-      <c r="AA19" s="43"/>
+      <c r="AA19" s="34"/>
       <c r="AB19" s="12"/>
       <c r="AC19" s="12"/>
       <c r="AD19" s="12"/>
       <c r="AE19" s="12"/>
-      <c r="AF19" s="42"/>
+      <c r="AF19" s="38"/>
       <c r="AG19" s="12"/>
       <c r="AH19" s="12"/>
-      <c r="AI19" s="43"/>
+      <c r="AI19" s="34"/>
       <c r="AJ19" s="12"/>
       <c r="AK19" s="5">
         <f t="shared" si="2"/>
@@ -2484,36 +2484,36 @@
       <c r="E20" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="43"/>
+      <c r="F20" s="34"/>
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
-      <c r="K20" s="42"/>
+      <c r="K20" s="38"/>
       <c r="L20" s="12"/>
-      <c r="M20" s="43"/>
+      <c r="M20" s="34"/>
       <c r="N20" s="12"/>
       <c r="O20" s="12"/>
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
-      <c r="R20" s="42"/>
+      <c r="R20" s="38"/>
       <c r="S20" s="12"/>
-      <c r="T20" s="43"/>
+      <c r="T20" s="34"/>
       <c r="U20" s="12"/>
       <c r="V20" s="12"/>
       <c r="W20" s="12"/>
       <c r="X20" s="12"/>
-      <c r="Y20" s="42"/>
+      <c r="Y20" s="38"/>
       <c r="Z20" s="12"/>
-      <c r="AA20" s="43"/>
+      <c r="AA20" s="34"/>
       <c r="AB20" s="12"/>
       <c r="AC20" s="12"/>
       <c r="AD20" s="12"/>
       <c r="AE20" s="12"/>
-      <c r="AF20" s="42"/>
+      <c r="AF20" s="38"/>
       <c r="AG20" s="12"/>
       <c r="AH20" s="12"/>
-      <c r="AI20" s="43"/>
+      <c r="AI20" s="34"/>
       <c r="AJ20" s="12"/>
       <c r="AK20" s="5">
         <f t="shared" si="2"/>
@@ -2555,36 +2555,36 @@
       <c r="E21" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="43"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
-      <c r="K21" s="42"/>
+      <c r="K21" s="38"/>
       <c r="L21" s="12"/>
-      <c r="M21" s="43"/>
+      <c r="M21" s="34"/>
       <c r="N21" s="12"/>
       <c r="O21" s="12"/>
       <c r="P21" s="12"/>
       <c r="Q21" s="12"/>
-      <c r="R21" s="42"/>
+      <c r="R21" s="38"/>
       <c r="S21" s="12"/>
-      <c r="T21" s="43"/>
+      <c r="T21" s="34"/>
       <c r="U21" s="12"/>
       <c r="V21" s="12"/>
       <c r="W21" s="12"/>
       <c r="X21" s="12"/>
-      <c r="Y21" s="42"/>
+      <c r="Y21" s="38"/>
       <c r="Z21" s="12"/>
-      <c r="AA21" s="43"/>
+      <c r="AA21" s="34"/>
       <c r="AB21" s="12"/>
       <c r="AC21" s="12"/>
       <c r="AD21" s="12"/>
       <c r="AE21" s="12"/>
-      <c r="AF21" s="42"/>
+      <c r="AF21" s="38"/>
       <c r="AG21" s="12"/>
       <c r="AH21" s="12"/>
-      <c r="AI21" s="43"/>
+      <c r="AI21" s="34"/>
       <c r="AJ21" s="12"/>
       <c r="AK21" s="5">
         <f t="shared" si="2"/>
@@ -2611,36 +2611,36 @@
       <c r="E22" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="43"/>
+      <c r="F22" s="34"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
-      <c r="K22" s="42"/>
+      <c r="K22" s="38"/>
       <c r="L22" s="12"/>
-      <c r="M22" s="43"/>
+      <c r="M22" s="34"/>
       <c r="N22" s="12"/>
       <c r="O22" s="12"/>
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
-      <c r="R22" s="42"/>
+      <c r="R22" s="38"/>
       <c r="S22" s="12"/>
-      <c r="T22" s="43"/>
+      <c r="T22" s="34"/>
       <c r="U22" s="12"/>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
       <c r="X22" s="12"/>
-      <c r="Y22" s="42"/>
+      <c r="Y22" s="38"/>
       <c r="Z22" s="12"/>
-      <c r="AA22" s="43"/>
+      <c r="AA22" s="34"/>
       <c r="AB22" s="12"/>
       <c r="AC22" s="12"/>
       <c r="AD22" s="12"/>
       <c r="AE22" s="12"/>
-      <c r="AF22" s="42"/>
+      <c r="AF22" s="38"/>
       <c r="AG22" s="12"/>
       <c r="AH22" s="12"/>
-      <c r="AI22" s="43"/>
+      <c r="AI22" s="34"/>
       <c r="AJ22" s="12"/>
       <c r="AK22" s="5">
         <f t="shared" si="2"/>
@@ -2667,36 +2667,36 @@
       <c r="E23" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="43"/>
+      <c r="F23" s="34"/>
       <c r="G23" s="12"/>
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
-      <c r="K23" s="42"/>
+      <c r="K23" s="38"/>
       <c r="L23" s="12"/>
-      <c r="M23" s="43"/>
+      <c r="M23" s="34"/>
       <c r="N23" s="12"/>
       <c r="O23" s="12"/>
       <c r="P23" s="12"/>
       <c r="Q23" s="12"/>
-      <c r="R23" s="42"/>
+      <c r="R23" s="38"/>
       <c r="S23" s="12"/>
-      <c r="T23" s="43"/>
+      <c r="T23" s="34"/>
       <c r="U23" s="12"/>
       <c r="V23" s="12"/>
       <c r="W23" s="12"/>
       <c r="X23" s="12"/>
-      <c r="Y23" s="42"/>
+      <c r="Y23" s="38"/>
       <c r="Z23" s="12"/>
-      <c r="AA23" s="43"/>
+      <c r="AA23" s="34"/>
       <c r="AB23" s="12"/>
       <c r="AC23" s="12"/>
       <c r="AD23" s="12"/>
       <c r="AE23" s="12"/>
-      <c r="AF23" s="42"/>
+      <c r="AF23" s="38"/>
       <c r="AG23" s="12"/>
       <c r="AH23" s="12"/>
-      <c r="AI23" s="43"/>
+      <c r="AI23" s="34"/>
       <c r="AJ23" s="12"/>
       <c r="AK23" s="5">
         <f t="shared" si="2"/>
@@ -2723,36 +2723,36 @@
       <c r="E24" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="43"/>
+      <c r="F24" s="34"/>
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
-      <c r="K24" s="42"/>
+      <c r="K24" s="38"/>
       <c r="L24" s="12"/>
-      <c r="M24" s="43"/>
+      <c r="M24" s="34"/>
       <c r="N24" s="12"/>
       <c r="O24" s="12"/>
       <c r="P24" s="12"/>
       <c r="Q24" s="12"/>
-      <c r="R24" s="42"/>
+      <c r="R24" s="38"/>
       <c r="S24" s="12"/>
-      <c r="T24" s="43"/>
+      <c r="T24" s="34"/>
       <c r="U24" s="12"/>
       <c r="V24" s="12"/>
       <c r="W24" s="12"/>
       <c r="X24" s="12"/>
-      <c r="Y24" s="42"/>
+      <c r="Y24" s="38"/>
       <c r="Z24" s="12"/>
-      <c r="AA24" s="43"/>
+      <c r="AA24" s="34"/>
       <c r="AB24" s="12"/>
       <c r="AC24" s="12"/>
       <c r="AD24" s="12"/>
       <c r="AE24" s="12"/>
-      <c r="AF24" s="42"/>
+      <c r="AF24" s="38"/>
       <c r="AG24" s="12"/>
       <c r="AH24" s="12"/>
-      <c r="AI24" s="43"/>
+      <c r="AI24" s="34"/>
       <c r="AJ24" s="12"/>
       <c r="AK24" s="5">
         <f t="shared" si="2"/>
@@ -2779,36 +2779,36 @@
       <c r="E25" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="43"/>
+      <c r="F25" s="34"/>
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
-      <c r="K25" s="42"/>
+      <c r="K25" s="38"/>
       <c r="L25" s="12"/>
-      <c r="M25" s="43"/>
+      <c r="M25" s="34"/>
       <c r="N25" s="12"/>
       <c r="O25" s="12"/>
       <c r="P25" s="12"/>
       <c r="Q25" s="12"/>
-      <c r="R25" s="42"/>
+      <c r="R25" s="38"/>
       <c r="S25" s="12"/>
-      <c r="T25" s="43"/>
+      <c r="T25" s="34"/>
       <c r="U25" s="12"/>
       <c r="V25" s="12"/>
       <c r="W25" s="12"/>
       <c r="X25" s="12"/>
-      <c r="Y25" s="42"/>
+      <c r="Y25" s="38"/>
       <c r="Z25" s="12"/>
-      <c r="AA25" s="43"/>
+      <c r="AA25" s="34"/>
       <c r="AB25" s="12"/>
       <c r="AC25" s="12"/>
       <c r="AD25" s="12"/>
       <c r="AE25" s="12"/>
-      <c r="AF25" s="42"/>
+      <c r="AF25" s="38"/>
       <c r="AG25" s="12"/>
       <c r="AH25" s="12"/>
-      <c r="AI25" s="43"/>
+      <c r="AI25" s="34"/>
       <c r="AJ25" s="12"/>
       <c r="AK25" s="5">
         <f t="shared" si="2"/>
@@ -2835,36 +2835,36 @@
       <c r="E26" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="43"/>
+      <c r="F26" s="34"/>
       <c r="G26" s="12"/>
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
-      <c r="K26" s="42"/>
+      <c r="K26" s="38"/>
       <c r="L26" s="12"/>
-      <c r="M26" s="43"/>
+      <c r="M26" s="34"/>
       <c r="N26" s="12"/>
       <c r="O26" s="12"/>
       <c r="P26" s="12"/>
       <c r="Q26" s="12"/>
-      <c r="R26" s="42"/>
+      <c r="R26" s="38"/>
       <c r="S26" s="12"/>
-      <c r="T26" s="43"/>
+      <c r="T26" s="34"/>
       <c r="U26" s="12"/>
       <c r="V26" s="12"/>
       <c r="W26" s="12"/>
       <c r="X26" s="12"/>
-      <c r="Y26" s="42"/>
+      <c r="Y26" s="38"/>
       <c r="Z26" s="12"/>
-      <c r="AA26" s="43"/>
+      <c r="AA26" s="34"/>
       <c r="AB26" s="12"/>
       <c r="AC26" s="12"/>
       <c r="AD26" s="12"/>
       <c r="AE26" s="12"/>
-      <c r="AF26" s="42"/>
+      <c r="AF26" s="38"/>
       <c r="AG26" s="12"/>
       <c r="AH26" s="12"/>
-      <c r="AI26" s="43"/>
+      <c r="AI26" s="34"/>
       <c r="AJ26" s="12"/>
       <c r="AK26" s="5">
         <f t="shared" si="2"/>
@@ -2891,36 +2891,36 @@
       <c r="E27" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="43"/>
+      <c r="F27" s="34"/>
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
-      <c r="K27" s="42"/>
+      <c r="K27" s="38"/>
       <c r="L27" s="12"/>
-      <c r="M27" s="43"/>
+      <c r="M27" s="34"/>
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
       <c r="P27" s="12"/>
       <c r="Q27" s="12"/>
-      <c r="R27" s="42"/>
+      <c r="R27" s="38"/>
       <c r="S27" s="12"/>
-      <c r="T27" s="43"/>
+      <c r="T27" s="34"/>
       <c r="U27" s="12"/>
       <c r="V27" s="12"/>
       <c r="W27" s="12"/>
       <c r="X27" s="12"/>
-      <c r="Y27" s="42"/>
+      <c r="Y27" s="38"/>
       <c r="Z27" s="12"/>
-      <c r="AA27" s="43"/>
+      <c r="AA27" s="34"/>
       <c r="AB27" s="12"/>
       <c r="AC27" s="12"/>
       <c r="AD27" s="12"/>
       <c r="AE27" s="12"/>
-      <c r="AF27" s="42"/>
+      <c r="AF27" s="38"/>
       <c r="AG27" s="12"/>
       <c r="AH27" s="12"/>
-      <c r="AI27" s="43"/>
+      <c r="AI27" s="34"/>
       <c r="AJ27" s="12"/>
       <c r="AK27" s="5">
         <f t="shared" si="2"/>
@@ -2947,36 +2947,36 @@
       <c r="E28" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="43"/>
+      <c r="F28" s="34"/>
       <c r="G28" s="12"/>
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
-      <c r="K28" s="42"/>
+      <c r="K28" s="38"/>
       <c r="L28" s="12"/>
-      <c r="M28" s="43"/>
+      <c r="M28" s="34"/>
       <c r="N28" s="12"/>
       <c r="O28" s="12"/>
       <c r="P28" s="12"/>
       <c r="Q28" s="12"/>
-      <c r="R28" s="42"/>
+      <c r="R28" s="38"/>
       <c r="S28" s="12"/>
-      <c r="T28" s="43"/>
+      <c r="T28" s="34"/>
       <c r="U28" s="12"/>
       <c r="V28" s="12"/>
       <c r="W28" s="12"/>
       <c r="X28" s="12"/>
-      <c r="Y28" s="42"/>
+      <c r="Y28" s="38"/>
       <c r="Z28" s="12"/>
-      <c r="AA28" s="43"/>
+      <c r="AA28" s="34"/>
       <c r="AB28" s="12"/>
       <c r="AC28" s="12"/>
       <c r="AD28" s="12"/>
       <c r="AE28" s="12"/>
-      <c r="AF28" s="42"/>
+      <c r="AF28" s="38"/>
       <c r="AG28" s="12"/>
       <c r="AH28" s="12"/>
-      <c r="AI28" s="43"/>
+      <c r="AI28" s="34"/>
       <c r="AJ28" s="12"/>
       <c r="AK28" s="5">
         <f t="shared" si="2"/>
@@ -3003,36 +3003,36 @@
       <c r="E29" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="43"/>
+      <c r="F29" s="34"/>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
-      <c r="K29" s="42"/>
+      <c r="K29" s="38"/>
       <c r="L29" s="12"/>
-      <c r="M29" s="43"/>
+      <c r="M29" s="34"/>
       <c r="N29" s="12"/>
       <c r="O29" s="12"/>
       <c r="P29" s="12"/>
       <c r="Q29" s="12"/>
-      <c r="R29" s="42"/>
+      <c r="R29" s="38"/>
       <c r="S29" s="12"/>
-      <c r="T29" s="43"/>
+      <c r="T29" s="34"/>
       <c r="U29" s="12"/>
       <c r="V29" s="12"/>
       <c r="W29" s="12"/>
       <c r="X29" s="12"/>
-      <c r="Y29" s="42"/>
+      <c r="Y29" s="38"/>
       <c r="Z29" s="12"/>
-      <c r="AA29" s="43"/>
+      <c r="AA29" s="34"/>
       <c r="AB29" s="12"/>
       <c r="AC29" s="12"/>
       <c r="AD29" s="12"/>
       <c r="AE29" s="12"/>
-      <c r="AF29" s="42"/>
+      <c r="AF29" s="38"/>
       <c r="AG29" s="12"/>
       <c r="AH29" s="12"/>
-      <c r="AI29" s="43"/>
+      <c r="AI29" s="34"/>
       <c r="AJ29" s="12"/>
       <c r="AK29" s="5">
         <f t="shared" si="2"/>
@@ -3059,36 +3059,36 @@
       <c r="E30" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="43"/>
+      <c r="F30" s="34"/>
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
-      <c r="K30" s="42"/>
+      <c r="K30" s="38"/>
       <c r="L30" s="12"/>
-      <c r="M30" s="43"/>
+      <c r="M30" s="34"/>
       <c r="N30" s="12"/>
       <c r="O30" s="12"/>
       <c r="P30" s="12"/>
       <c r="Q30" s="12"/>
-      <c r="R30" s="42"/>
+      <c r="R30" s="38"/>
       <c r="S30" s="12"/>
-      <c r="T30" s="43"/>
+      <c r="T30" s="34"/>
       <c r="U30" s="12"/>
       <c r="V30" s="12"/>
       <c r="W30" s="12"/>
       <c r="X30" s="12"/>
-      <c r="Y30" s="42"/>
+      <c r="Y30" s="38"/>
       <c r="Z30" s="12"/>
-      <c r="AA30" s="43"/>
+      <c r="AA30" s="34"/>
       <c r="AB30" s="12"/>
       <c r="AC30" s="12"/>
       <c r="AD30" s="12"/>
       <c r="AE30" s="12"/>
-      <c r="AF30" s="42"/>
+      <c r="AF30" s="38"/>
       <c r="AG30" s="12"/>
       <c r="AH30" s="12"/>
-      <c r="AI30" s="43"/>
+      <c r="AI30" s="34"/>
       <c r="AJ30" s="12"/>
       <c r="AK30" s="5">
         <f t="shared" si="2"/>
@@ -3115,36 +3115,36 @@
       <c r="E31" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="43"/>
+      <c r="F31" s="34"/>
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
-      <c r="K31" s="42"/>
+      <c r="K31" s="38"/>
       <c r="L31" s="12"/>
-      <c r="M31" s="43"/>
+      <c r="M31" s="34"/>
       <c r="N31" s="12"/>
       <c r="O31" s="12"/>
       <c r="P31" s="12"/>
       <c r="Q31" s="12"/>
-      <c r="R31" s="42"/>
+      <c r="R31" s="38"/>
       <c r="S31" s="12"/>
-      <c r="T31" s="43"/>
+      <c r="T31" s="34"/>
       <c r="U31" s="12"/>
       <c r="V31" s="12"/>
       <c r="W31" s="12"/>
       <c r="X31" s="12"/>
-      <c r="Y31" s="42"/>
+      <c r="Y31" s="38"/>
       <c r="Z31" s="12"/>
-      <c r="AA31" s="43"/>
+      <c r="AA31" s="34"/>
       <c r="AB31" s="12"/>
       <c r="AC31" s="12"/>
       <c r="AD31" s="12"/>
       <c r="AE31" s="12"/>
-      <c r="AF31" s="42"/>
+      <c r="AF31" s="38"/>
       <c r="AG31" s="12"/>
       <c r="AH31" s="12"/>
-      <c r="AI31" s="43"/>
+      <c r="AI31" s="34"/>
       <c r="AJ31" s="12"/>
       <c r="AK31" s="5">
         <f t="shared" si="2"/>
@@ -3171,36 +3171,36 @@
       <c r="E32" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="43"/>
+      <c r="F32" s="34"/>
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
       <c r="J32" s="12"/>
-      <c r="K32" s="42"/>
+      <c r="K32" s="38"/>
       <c r="L32" s="12"/>
-      <c r="M32" s="43"/>
+      <c r="M32" s="34"/>
       <c r="N32" s="12"/>
       <c r="O32" s="12"/>
       <c r="P32" s="12"/>
       <c r="Q32" s="12"/>
-      <c r="R32" s="42"/>
+      <c r="R32" s="38"/>
       <c r="S32" s="12"/>
-      <c r="T32" s="43"/>
+      <c r="T32" s="34"/>
       <c r="U32" s="12"/>
       <c r="V32" s="12"/>
       <c r="W32" s="12"/>
       <c r="X32" s="12"/>
-      <c r="Y32" s="42"/>
+      <c r="Y32" s="38"/>
       <c r="Z32" s="12"/>
-      <c r="AA32" s="43"/>
+      <c r="AA32" s="34"/>
       <c r="AB32" s="12"/>
       <c r="AC32" s="12"/>
       <c r="AD32" s="12"/>
       <c r="AE32" s="12"/>
-      <c r="AF32" s="42"/>
+      <c r="AF32" s="38"/>
       <c r="AG32" s="12"/>
       <c r="AH32" s="12"/>
-      <c r="AI32" s="43"/>
+      <c r="AI32" s="34"/>
       <c r="AJ32" s="12"/>
       <c r="AK32" s="5">
         <f t="shared" si="2"/>
@@ -3227,36 +3227,36 @@
       <c r="E33" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="43"/>
+      <c r="F33" s="34"/>
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
-      <c r="K33" s="42"/>
+      <c r="K33" s="38"/>
       <c r="L33" s="12"/>
-      <c r="M33" s="43"/>
+      <c r="M33" s="34"/>
       <c r="N33" s="12"/>
       <c r="O33" s="12"/>
       <c r="P33" s="12"/>
       <c r="Q33" s="12"/>
-      <c r="R33" s="42"/>
+      <c r="R33" s="38"/>
       <c r="S33" s="12"/>
-      <c r="T33" s="43"/>
+      <c r="T33" s="34"/>
       <c r="U33" s="12"/>
       <c r="V33" s="12"/>
       <c r="W33" s="12"/>
       <c r="X33" s="12"/>
-      <c r="Y33" s="42"/>
+      <c r="Y33" s="38"/>
       <c r="Z33" s="12"/>
-      <c r="AA33" s="43"/>
+      <c r="AA33" s="34"/>
       <c r="AB33" s="12"/>
       <c r="AC33" s="12"/>
       <c r="AD33" s="12"/>
       <c r="AE33" s="12"/>
-      <c r="AF33" s="42"/>
+      <c r="AF33" s="38"/>
       <c r="AG33" s="12"/>
       <c r="AH33" s="12"/>
-      <c r="AI33" s="43"/>
+      <c r="AI33" s="34"/>
       <c r="AJ33" s="12"/>
       <c r="AK33" s="5">
         <f t="shared" si="2"/>
@@ -3283,36 +3283,36 @@
       <c r="E34" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F34" s="43"/>
+      <c r="F34" s="34"/>
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
-      <c r="K34" s="42"/>
+      <c r="K34" s="38"/>
       <c r="L34" s="12"/>
-      <c r="M34" s="43"/>
+      <c r="M34" s="34"/>
       <c r="N34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="12"/>
       <c r="Q34" s="12"/>
-      <c r="R34" s="42"/>
+      <c r="R34" s="38"/>
       <c r="S34" s="12"/>
-      <c r="T34" s="43"/>
+      <c r="T34" s="34"/>
       <c r="U34" s="12"/>
       <c r="V34" s="12"/>
       <c r="W34" s="12"/>
       <c r="X34" s="12"/>
-      <c r="Y34" s="42"/>
+      <c r="Y34" s="38"/>
       <c r="Z34" s="12"/>
-      <c r="AA34" s="43"/>
+      <c r="AA34" s="34"/>
       <c r="AB34" s="12"/>
       <c r="AC34" s="12"/>
       <c r="AD34" s="12"/>
       <c r="AE34" s="12"/>
-      <c r="AF34" s="42"/>
+      <c r="AF34" s="38"/>
       <c r="AG34" s="12"/>
       <c r="AH34" s="12"/>
-      <c r="AI34" s="43"/>
+      <c r="AI34" s="34"/>
       <c r="AJ34" s="12"/>
       <c r="AK34" s="5">
         <f t="shared" si="2"/>
@@ -3339,36 +3339,36 @@
       <c r="E35" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F35" s="43"/>
+      <c r="F35" s="34"/>
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
-      <c r="K35" s="42"/>
+      <c r="K35" s="38"/>
       <c r="L35" s="12"/>
-      <c r="M35" s="43"/>
+      <c r="M35" s="34"/>
       <c r="N35" s="12"/>
       <c r="O35" s="12"/>
       <c r="P35" s="12"/>
       <c r="Q35" s="12"/>
-      <c r="R35" s="42"/>
+      <c r="R35" s="38"/>
       <c r="S35" s="12"/>
-      <c r="T35" s="43"/>
+      <c r="T35" s="34"/>
       <c r="U35" s="12"/>
       <c r="V35" s="12"/>
       <c r="W35" s="12"/>
       <c r="X35" s="12"/>
-      <c r="Y35" s="42"/>
+      <c r="Y35" s="38"/>
       <c r="Z35" s="12"/>
-      <c r="AA35" s="43"/>
+      <c r="AA35" s="34"/>
       <c r="AB35" s="12"/>
       <c r="AC35" s="12"/>
       <c r="AD35" s="12"/>
       <c r="AE35" s="12"/>
-      <c r="AF35" s="42"/>
+      <c r="AF35" s="38"/>
       <c r="AG35" s="12"/>
       <c r="AH35" s="12"/>
-      <c r="AI35" s="43"/>
+      <c r="AI35" s="34"/>
       <c r="AJ35" s="12"/>
       <c r="AK35" s="5">
         <f t="shared" ref="AK35:AK52" si="4">COUNTIF(F35:AJ35,"P")</f>
@@ -3395,36 +3395,36 @@
       <c r="E36" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F36" s="43"/>
+      <c r="F36" s="34"/>
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
-      <c r="K36" s="42"/>
+      <c r="K36" s="38"/>
       <c r="L36" s="12"/>
-      <c r="M36" s="43"/>
+      <c r="M36" s="34"/>
       <c r="N36" s="12"/>
       <c r="O36" s="12"/>
       <c r="P36" s="12"/>
       <c r="Q36" s="12"/>
-      <c r="R36" s="42"/>
+      <c r="R36" s="38"/>
       <c r="S36" s="12"/>
-      <c r="T36" s="43"/>
+      <c r="T36" s="34"/>
       <c r="U36" s="12"/>
       <c r="V36" s="12"/>
       <c r="W36" s="12"/>
       <c r="X36" s="12"/>
-      <c r="Y36" s="42"/>
+      <c r="Y36" s="38"/>
       <c r="Z36" s="12"/>
-      <c r="AA36" s="43"/>
+      <c r="AA36" s="34"/>
       <c r="AB36" s="12"/>
       <c r="AC36" s="12"/>
       <c r="AD36" s="12"/>
       <c r="AE36" s="12"/>
-      <c r="AF36" s="42"/>
+      <c r="AF36" s="38"/>
       <c r="AG36" s="12"/>
       <c r="AH36" s="12"/>
-      <c r="AI36" s="43"/>
+      <c r="AI36" s="34"/>
       <c r="AJ36" s="12"/>
       <c r="AK36" s="5">
         <f t="shared" si="4"/>
@@ -3451,36 +3451,36 @@
       <c r="E37" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F37" s="43"/>
+      <c r="F37" s="34"/>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
-      <c r="K37" s="42"/>
+      <c r="K37" s="38"/>
       <c r="L37" s="12"/>
-      <c r="M37" s="43"/>
+      <c r="M37" s="34"/>
       <c r="N37" s="12"/>
       <c r="O37" s="12"/>
       <c r="P37" s="12"/>
       <c r="Q37" s="12"/>
-      <c r="R37" s="42"/>
+      <c r="R37" s="38"/>
       <c r="S37" s="12"/>
-      <c r="T37" s="43"/>
+      <c r="T37" s="34"/>
       <c r="U37" s="12"/>
       <c r="V37" s="12"/>
       <c r="W37" s="12"/>
       <c r="X37" s="12"/>
-      <c r="Y37" s="42"/>
+      <c r="Y37" s="38"/>
       <c r="Z37" s="12"/>
-      <c r="AA37" s="43"/>
+      <c r="AA37" s="34"/>
       <c r="AB37" s="12"/>
       <c r="AC37" s="12"/>
       <c r="AD37" s="12"/>
       <c r="AE37" s="12"/>
-      <c r="AF37" s="42"/>
+      <c r="AF37" s="38"/>
       <c r="AG37" s="12"/>
       <c r="AH37" s="12"/>
-      <c r="AI37" s="43"/>
+      <c r="AI37" s="34"/>
       <c r="AJ37" s="12"/>
       <c r="AK37" s="5">
         <f t="shared" si="4"/>
@@ -3507,36 +3507,36 @@
       <c r="E38" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F38" s="43"/>
+      <c r="F38" s="34"/>
       <c r="G38" s="12"/>
       <c r="H38" s="12"/>
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
-      <c r="K38" s="42"/>
+      <c r="K38" s="38"/>
       <c r="L38" s="12"/>
-      <c r="M38" s="43"/>
+      <c r="M38" s="34"/>
       <c r="N38" s="12"/>
       <c r="O38" s="12"/>
       <c r="P38" s="12"/>
       <c r="Q38" s="12"/>
-      <c r="R38" s="42"/>
+      <c r="R38" s="38"/>
       <c r="S38" s="12"/>
-      <c r="T38" s="43"/>
+      <c r="T38" s="34"/>
       <c r="U38" s="12"/>
       <c r="V38" s="12"/>
       <c r="W38" s="12"/>
       <c r="X38" s="12"/>
-      <c r="Y38" s="42"/>
+      <c r="Y38" s="38"/>
       <c r="Z38" s="12"/>
-      <c r="AA38" s="43"/>
+      <c r="AA38" s="34"/>
       <c r="AB38" s="12"/>
       <c r="AC38" s="12"/>
       <c r="AD38" s="12"/>
       <c r="AE38" s="12"/>
-      <c r="AF38" s="42"/>
+      <c r="AF38" s="38"/>
       <c r="AG38" s="12"/>
       <c r="AH38" s="12"/>
-      <c r="AI38" s="43"/>
+      <c r="AI38" s="34"/>
       <c r="AJ38" s="12"/>
       <c r="AK38" s="5">
         <f t="shared" si="4"/>
@@ -3563,36 +3563,36 @@
       <c r="E39" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F39" s="43"/>
+      <c r="F39" s="34"/>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
       <c r="I39" s="12"/>
       <c r="J39" s="12"/>
-      <c r="K39" s="42"/>
+      <c r="K39" s="38"/>
       <c r="L39" s="12"/>
-      <c r="M39" s="43"/>
+      <c r="M39" s="34"/>
       <c r="N39" s="12"/>
       <c r="O39" s="12"/>
       <c r="P39" s="12"/>
       <c r="Q39" s="12"/>
-      <c r="R39" s="42"/>
+      <c r="R39" s="38"/>
       <c r="S39" s="12"/>
-      <c r="T39" s="43"/>
+      <c r="T39" s="34"/>
       <c r="U39" s="12"/>
       <c r="V39" s="12"/>
       <c r="W39" s="12"/>
       <c r="X39" s="12"/>
-      <c r="Y39" s="42"/>
+      <c r="Y39" s="38"/>
       <c r="Z39" s="12"/>
-      <c r="AA39" s="43"/>
+      <c r="AA39" s="34"/>
       <c r="AB39" s="12"/>
       <c r="AC39" s="12"/>
       <c r="AD39" s="12"/>
       <c r="AE39" s="12"/>
-      <c r="AF39" s="42"/>
+      <c r="AF39" s="38"/>
       <c r="AG39" s="12"/>
       <c r="AH39" s="12"/>
-      <c r="AI39" s="43"/>
+      <c r="AI39" s="34"/>
       <c r="AJ39" s="12"/>
       <c r="AK39" s="5">
         <f t="shared" si="4"/>
@@ -3619,36 +3619,36 @@
       <c r="E40" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F40" s="43"/>
+      <c r="F40" s="34"/>
       <c r="G40" s="12"/>
       <c r="H40" s="12"/>
       <c r="I40" s="12"/>
       <c r="J40" s="12"/>
-      <c r="K40" s="42"/>
+      <c r="K40" s="38"/>
       <c r="L40" s="12"/>
-      <c r="M40" s="43"/>
+      <c r="M40" s="34"/>
       <c r="N40" s="12"/>
       <c r="O40" s="12"/>
       <c r="P40" s="12"/>
       <c r="Q40" s="12"/>
-      <c r="R40" s="42"/>
+      <c r="R40" s="38"/>
       <c r="S40" s="12"/>
-      <c r="T40" s="43"/>
+      <c r="T40" s="34"/>
       <c r="U40" s="12"/>
       <c r="V40" s="12"/>
       <c r="W40" s="12"/>
       <c r="X40" s="12"/>
-      <c r="Y40" s="42"/>
+      <c r="Y40" s="38"/>
       <c r="Z40" s="12"/>
-      <c r="AA40" s="43"/>
+      <c r="AA40" s="34"/>
       <c r="AB40" s="12"/>
       <c r="AC40" s="12"/>
       <c r="AD40" s="12"/>
       <c r="AE40" s="12"/>
-      <c r="AF40" s="42"/>
+      <c r="AF40" s="38"/>
       <c r="AG40" s="12"/>
       <c r="AH40" s="12"/>
-      <c r="AI40" s="43"/>
+      <c r="AI40" s="34"/>
       <c r="AJ40" s="12"/>
       <c r="AK40" s="5">
         <f t="shared" si="4"/>
@@ -3673,36 +3673,36 @@
       <c r="E41" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="43"/>
+      <c r="F41" s="34"/>
       <c r="G41" s="12"/>
       <c r="H41" s="12"/>
       <c r="I41" s="12"/>
       <c r="J41" s="12"/>
-      <c r="K41" s="42"/>
+      <c r="K41" s="38"/>
       <c r="L41" s="12"/>
-      <c r="M41" s="43"/>
+      <c r="M41" s="34"/>
       <c r="N41" s="12"/>
       <c r="O41" s="12"/>
       <c r="P41" s="12"/>
       <c r="Q41" s="12"/>
-      <c r="R41" s="42"/>
+      <c r="R41" s="38"/>
       <c r="S41" s="12"/>
-      <c r="T41" s="43"/>
+      <c r="T41" s="34"/>
       <c r="U41" s="12"/>
       <c r="V41" s="12"/>
       <c r="W41" s="12"/>
       <c r="X41" s="12"/>
-      <c r="Y41" s="42"/>
+      <c r="Y41" s="38"/>
       <c r="Z41" s="12"/>
-      <c r="AA41" s="43"/>
+      <c r="AA41" s="34"/>
       <c r="AB41" s="12"/>
       <c r="AC41" s="12"/>
       <c r="AD41" s="12"/>
       <c r="AE41" s="12"/>
-      <c r="AF41" s="42"/>
+      <c r="AF41" s="38"/>
       <c r="AG41" s="12"/>
       <c r="AH41" s="12"/>
-      <c r="AI41" s="43"/>
+      <c r="AI41" s="34"/>
       <c r="AJ41" s="12"/>
       <c r="AK41" s="5">
         <f t="shared" si="4"/>
@@ -3729,36 +3729,36 @@
       <c r="E42" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F42" s="43"/>
+      <c r="F42" s="34"/>
       <c r="G42" s="12"/>
       <c r="H42" s="12"/>
       <c r="I42" s="12"/>
       <c r="J42" s="12"/>
-      <c r="K42" s="42"/>
+      <c r="K42" s="38"/>
       <c r="L42" s="12"/>
-      <c r="M42" s="43"/>
+      <c r="M42" s="34"/>
       <c r="N42" s="12"/>
       <c r="O42" s="12"/>
       <c r="P42" s="12"/>
       <c r="Q42" s="12"/>
-      <c r="R42" s="42"/>
+      <c r="R42" s="38"/>
       <c r="S42" s="12"/>
-      <c r="T42" s="43"/>
+      <c r="T42" s="34"/>
       <c r="U42" s="12"/>
       <c r="V42" s="12"/>
       <c r="W42" s="12"/>
       <c r="X42" s="12"/>
-      <c r="Y42" s="42"/>
+      <c r="Y42" s="38"/>
       <c r="Z42" s="12"/>
-      <c r="AA42" s="43"/>
+      <c r="AA42" s="34"/>
       <c r="AB42" s="12"/>
       <c r="AC42" s="12"/>
       <c r="AD42" s="12"/>
       <c r="AE42" s="12"/>
-      <c r="AF42" s="42"/>
+      <c r="AF42" s="38"/>
       <c r="AG42" s="12"/>
       <c r="AH42" s="12"/>
-      <c r="AI42" s="43"/>
+      <c r="AI42" s="34"/>
       <c r="AJ42" s="12"/>
       <c r="AK42" s="5">
         <f t="shared" si="4"/>
@@ -3785,36 +3785,36 @@
       <c r="E43" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="43"/>
+      <c r="F43" s="34"/>
       <c r="G43" s="12"/>
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
       <c r="J43" s="12"/>
-      <c r="K43" s="42"/>
+      <c r="K43" s="38"/>
       <c r="L43" s="12"/>
-      <c r="M43" s="43"/>
+      <c r="M43" s="34"/>
       <c r="N43" s="12"/>
       <c r="O43" s="12"/>
       <c r="P43" s="12"/>
       <c r="Q43" s="12"/>
-      <c r="R43" s="42"/>
+      <c r="R43" s="38"/>
       <c r="S43" s="12"/>
-      <c r="T43" s="43"/>
+      <c r="T43" s="34"/>
       <c r="U43" s="12"/>
       <c r="V43" s="12"/>
       <c r="W43" s="12"/>
       <c r="X43" s="12"/>
-      <c r="Y43" s="42"/>
+      <c r="Y43" s="38"/>
       <c r="Z43" s="12"/>
-      <c r="AA43" s="43"/>
+      <c r="AA43" s="34"/>
       <c r="AB43" s="12"/>
       <c r="AC43" s="12"/>
       <c r="AD43" s="12"/>
       <c r="AE43" s="12"/>
-      <c r="AF43" s="42"/>
+      <c r="AF43" s="38"/>
       <c r="AG43" s="12"/>
       <c r="AH43" s="12"/>
-      <c r="AI43" s="43"/>
+      <c r="AI43" s="34"/>
       <c r="AJ43" s="12"/>
       <c r="AK43" s="5">
         <f t="shared" si="4"/>
@@ -3841,36 +3841,36 @@
       <c r="E44" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="43"/>
+      <c r="F44" s="34"/>
       <c r="G44" s="12"/>
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
       <c r="J44" s="12"/>
-      <c r="K44" s="42"/>
+      <c r="K44" s="38"/>
       <c r="L44" s="12"/>
-      <c r="M44" s="43"/>
+      <c r="M44" s="34"/>
       <c r="N44" s="12"/>
       <c r="O44" s="12"/>
       <c r="P44" s="12"/>
       <c r="Q44" s="12"/>
-      <c r="R44" s="42"/>
+      <c r="R44" s="38"/>
       <c r="S44" s="12"/>
-      <c r="T44" s="43"/>
+      <c r="T44" s="34"/>
       <c r="U44" s="12"/>
       <c r="V44" s="12"/>
       <c r="W44" s="12"/>
       <c r="X44" s="12"/>
-      <c r="Y44" s="42"/>
+      <c r="Y44" s="38"/>
       <c r="Z44" s="12"/>
-      <c r="AA44" s="43"/>
+      <c r="AA44" s="34"/>
       <c r="AB44" s="12"/>
       <c r="AC44" s="12"/>
       <c r="AD44" s="12"/>
       <c r="AE44" s="12"/>
-      <c r="AF44" s="42"/>
+      <c r="AF44" s="38"/>
       <c r="AG44" s="12"/>
       <c r="AH44" s="12"/>
-      <c r="AI44" s="43"/>
+      <c r="AI44" s="34"/>
       <c r="AJ44" s="12"/>
       <c r="AK44" s="5">
         <f t="shared" si="4"/>
@@ -3897,36 +3897,36 @@
       <c r="E45" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="43"/>
+      <c r="F45" s="34"/>
       <c r="G45" s="12"/>
       <c r="H45" s="12"/>
       <c r="I45" s="12"/>
       <c r="J45" s="12"/>
-      <c r="K45" s="42"/>
+      <c r="K45" s="38"/>
       <c r="L45" s="12"/>
-      <c r="M45" s="43"/>
+      <c r="M45" s="34"/>
       <c r="N45" s="12"/>
       <c r="O45" s="12"/>
       <c r="P45" s="12"/>
       <c r="Q45" s="12"/>
-      <c r="R45" s="42"/>
+      <c r="R45" s="38"/>
       <c r="S45" s="12"/>
-      <c r="T45" s="43"/>
+      <c r="T45" s="34"/>
       <c r="U45" s="12"/>
       <c r="V45" s="12"/>
       <c r="W45" s="12"/>
       <c r="X45" s="12"/>
-      <c r="Y45" s="42"/>
+      <c r="Y45" s="38"/>
       <c r="Z45" s="12"/>
-      <c r="AA45" s="43"/>
+      <c r="AA45" s="34"/>
       <c r="AB45" s="12"/>
       <c r="AC45" s="12"/>
       <c r="AD45" s="12"/>
       <c r="AE45" s="12"/>
-      <c r="AF45" s="42"/>
+      <c r="AF45" s="38"/>
       <c r="AG45" s="12"/>
       <c r="AH45" s="12"/>
-      <c r="AI45" s="43"/>
+      <c r="AI45" s="34"/>
       <c r="AJ45" s="12"/>
       <c r="AK45" s="5">
         <f t="shared" si="4"/>
@@ -3953,36 +3953,36 @@
       <c r="E46" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F46" s="43"/>
+      <c r="F46" s="34"/>
       <c r="G46" s="12"/>
       <c r="H46" s="12"/>
       <c r="I46" s="12"/>
       <c r="J46" s="12"/>
-      <c r="K46" s="42"/>
+      <c r="K46" s="38"/>
       <c r="L46" s="12"/>
-      <c r="M46" s="43"/>
+      <c r="M46" s="34"/>
       <c r="N46" s="12"/>
       <c r="O46" s="12"/>
       <c r="P46" s="12"/>
       <c r="Q46" s="12"/>
-      <c r="R46" s="42"/>
+      <c r="R46" s="38"/>
       <c r="S46" s="12"/>
-      <c r="T46" s="43"/>
+      <c r="T46" s="34"/>
       <c r="U46" s="12"/>
       <c r="V46" s="12"/>
       <c r="W46" s="12"/>
       <c r="X46" s="12"/>
-      <c r="Y46" s="42"/>
+      <c r="Y46" s="38"/>
       <c r="Z46" s="12"/>
-      <c r="AA46" s="43"/>
+      <c r="AA46" s="34"/>
       <c r="AB46" s="12"/>
       <c r="AC46" s="12"/>
       <c r="AD46" s="12"/>
       <c r="AE46" s="12"/>
-      <c r="AF46" s="42"/>
+      <c r="AF46" s="38"/>
       <c r="AG46" s="12"/>
       <c r="AH46" s="12"/>
-      <c r="AI46" s="43"/>
+      <c r="AI46" s="34"/>
       <c r="AJ46" s="12"/>
       <c r="AK46" s="5">
         <f t="shared" si="4"/>
@@ -4007,36 +4007,36 @@
       <c r="E47" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="43"/>
+      <c r="F47" s="34"/>
       <c r="G47" s="12"/>
       <c r="H47" s="12"/>
       <c r="I47" s="12"/>
       <c r="J47" s="12"/>
-      <c r="K47" s="42"/>
+      <c r="K47" s="38"/>
       <c r="L47" s="12"/>
-      <c r="M47" s="43"/>
+      <c r="M47" s="34"/>
       <c r="N47" s="12"/>
       <c r="O47" s="12"/>
       <c r="P47" s="12"/>
       <c r="Q47" s="12"/>
-      <c r="R47" s="42"/>
+      <c r="R47" s="38"/>
       <c r="S47" s="12"/>
-      <c r="T47" s="43"/>
+      <c r="T47" s="34"/>
       <c r="U47" s="12"/>
       <c r="V47" s="12"/>
       <c r="W47" s="12"/>
       <c r="X47" s="12"/>
-      <c r="Y47" s="42"/>
+      <c r="Y47" s="38"/>
       <c r="Z47" s="12"/>
-      <c r="AA47" s="43"/>
+      <c r="AA47" s="34"/>
       <c r="AB47" s="12"/>
       <c r="AC47" s="12"/>
       <c r="AD47" s="12"/>
       <c r="AE47" s="12"/>
-      <c r="AF47" s="42"/>
+      <c r="AF47" s="38"/>
       <c r="AG47" s="12"/>
       <c r="AH47" s="12"/>
-      <c r="AI47" s="43"/>
+      <c r="AI47" s="34"/>
       <c r="AJ47" s="12"/>
       <c r="AK47" s="5">
         <f t="shared" si="4"/>
@@ -4063,36 +4063,36 @@
       <c r="E48" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F48" s="43"/>
+      <c r="F48" s="34"/>
       <c r="G48" s="12"/>
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
-      <c r="K48" s="42"/>
+      <c r="K48" s="38"/>
       <c r="L48" s="12"/>
-      <c r="M48" s="43"/>
+      <c r="M48" s="34"/>
       <c r="N48" s="12"/>
       <c r="O48" s="12"/>
       <c r="P48" s="12"/>
       <c r="Q48" s="12"/>
-      <c r="R48" s="42"/>
+      <c r="R48" s="38"/>
       <c r="S48" s="12"/>
-      <c r="T48" s="43"/>
+      <c r="T48" s="34"/>
       <c r="U48" s="12"/>
       <c r="V48" s="12"/>
       <c r="W48" s="12"/>
       <c r="X48" s="12"/>
-      <c r="Y48" s="42"/>
+      <c r="Y48" s="38"/>
       <c r="Z48" s="12"/>
-      <c r="AA48" s="43"/>
+      <c r="AA48" s="34"/>
       <c r="AB48" s="12"/>
       <c r="AC48" s="12"/>
       <c r="AD48" s="12"/>
       <c r="AE48" s="12"/>
-      <c r="AF48" s="42"/>
+      <c r="AF48" s="38"/>
       <c r="AG48" s="12"/>
       <c r="AH48" s="12"/>
-      <c r="AI48" s="43"/>
+      <c r="AI48" s="34"/>
       <c r="AJ48" s="12"/>
       <c r="AK48" s="5">
         <f t="shared" si="4"/>
@@ -4117,36 +4117,36 @@
       <c r="E49" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="43"/>
+      <c r="F49" s="34"/>
       <c r="G49" s="12"/>
       <c r="H49" s="12"/>
       <c r="I49" s="12"/>
       <c r="J49" s="12"/>
-      <c r="K49" s="42"/>
+      <c r="K49" s="38"/>
       <c r="L49" s="12"/>
-      <c r="M49" s="43"/>
+      <c r="M49" s="34"/>
       <c r="N49" s="12"/>
       <c r="O49" s="12"/>
       <c r="P49" s="12"/>
       <c r="Q49" s="12"/>
-      <c r="R49" s="42"/>
+      <c r="R49" s="38"/>
       <c r="S49" s="12"/>
-      <c r="T49" s="43"/>
+      <c r="T49" s="34"/>
       <c r="U49" s="12"/>
       <c r="V49" s="12"/>
       <c r="W49" s="12"/>
       <c r="X49" s="12"/>
-      <c r="Y49" s="42"/>
+      <c r="Y49" s="38"/>
       <c r="Z49" s="12"/>
-      <c r="AA49" s="43"/>
+      <c r="AA49" s="34"/>
       <c r="AB49" s="12"/>
       <c r="AC49" s="12"/>
       <c r="AD49" s="12"/>
       <c r="AE49" s="12"/>
-      <c r="AF49" s="42"/>
+      <c r="AF49" s="38"/>
       <c r="AG49" s="12"/>
       <c r="AH49" s="12"/>
-      <c r="AI49" s="43"/>
+      <c r="AI49" s="34"/>
       <c r="AJ49" s="12"/>
       <c r="AK49" s="5">
         <f t="shared" si="4"/>
@@ -4171,36 +4171,36 @@
       <c r="E50" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="43"/>
+      <c r="F50" s="34"/>
       <c r="G50" s="29"/>
       <c r="H50" s="29"/>
       <c r="I50" s="29"/>
       <c r="J50" s="29"/>
-      <c r="K50" s="42"/>
+      <c r="K50" s="38"/>
       <c r="L50" s="29"/>
-      <c r="M50" s="43"/>
+      <c r="M50" s="34"/>
       <c r="N50" s="29"/>
       <c r="O50" s="29"/>
       <c r="P50" s="29"/>
       <c r="Q50" s="29"/>
-      <c r="R50" s="42"/>
+      <c r="R50" s="38"/>
       <c r="S50" s="29"/>
-      <c r="T50" s="43"/>
+      <c r="T50" s="34"/>
       <c r="U50" s="29"/>
       <c r="V50" s="29"/>
       <c r="W50" s="29"/>
       <c r="X50" s="29"/>
-      <c r="Y50" s="42"/>
+      <c r="Y50" s="38"/>
       <c r="Z50" s="29"/>
-      <c r="AA50" s="43"/>
+      <c r="AA50" s="34"/>
       <c r="AB50" s="12"/>
       <c r="AC50" s="29"/>
       <c r="AD50" s="29"/>
       <c r="AE50" s="29"/>
-      <c r="AF50" s="42"/>
+      <c r="AF50" s="38"/>
       <c r="AG50" s="12"/>
       <c r="AH50" s="12"/>
-      <c r="AI50" s="43"/>
+      <c r="AI50" s="34"/>
       <c r="AJ50" s="12"/>
       <c r="AK50" s="30">
         <f t="shared" si="4"/>
@@ -4225,36 +4225,36 @@
       <c r="E51" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="F51" s="43"/>
+      <c r="F51" s="34"/>
       <c r="G51" s="31"/>
       <c r="H51" s="31"/>
       <c r="I51" s="31"/>
       <c r="J51" s="31"/>
-      <c r="K51" s="42"/>
+      <c r="K51" s="38"/>
       <c r="L51" s="31"/>
-      <c r="M51" s="43"/>
+      <c r="M51" s="34"/>
       <c r="N51" s="31"/>
       <c r="O51" s="31"/>
       <c r="P51" s="31"/>
       <c r="Q51" s="31"/>
-      <c r="R51" s="42"/>
+      <c r="R51" s="38"/>
       <c r="S51" s="31"/>
-      <c r="T51" s="43"/>
+      <c r="T51" s="34"/>
       <c r="U51" s="31"/>
       <c r="V51" s="31"/>
       <c r="W51" s="31"/>
       <c r="X51" s="31"/>
-      <c r="Y51" s="42"/>
+      <c r="Y51" s="38"/>
       <c r="Z51" s="31"/>
-      <c r="AA51" s="43"/>
+      <c r="AA51" s="34"/>
       <c r="AB51" s="12"/>
       <c r="AC51" s="29"/>
       <c r="AD51" s="29"/>
       <c r="AE51" s="29"/>
-      <c r="AF51" s="42"/>
+      <c r="AF51" s="38"/>
       <c r="AG51" s="12"/>
       <c r="AH51" s="12"/>
-      <c r="AI51" s="43"/>
+      <c r="AI51" s="34"/>
       <c r="AJ51" s="12"/>
       <c r="AK51" s="30">
         <f t="shared" si="4"/>
@@ -4279,36 +4279,36 @@
       <c r="E52" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="43"/>
+      <c r="F52" s="34"/>
       <c r="G52" s="31"/>
       <c r="H52" s="31"/>
       <c r="I52" s="31"/>
       <c r="J52" s="31"/>
-      <c r="K52" s="42"/>
+      <c r="K52" s="38"/>
       <c r="L52" s="31"/>
-      <c r="M52" s="43"/>
+      <c r="M52" s="34"/>
       <c r="N52" s="31"/>
       <c r="O52" s="31"/>
       <c r="P52" s="31"/>
       <c r="Q52" s="31"/>
-      <c r="R52" s="42"/>
+      <c r="R52" s="38"/>
       <c r="S52" s="31"/>
-      <c r="T52" s="43"/>
+      <c r="T52" s="34"/>
       <c r="U52" s="31"/>
       <c r="V52" s="31"/>
       <c r="W52" s="31"/>
       <c r="X52" s="31"/>
-      <c r="Y52" s="42"/>
+      <c r="Y52" s="38"/>
       <c r="Z52" s="31"/>
-      <c r="AA52" s="43"/>
+      <c r="AA52" s="34"/>
       <c r="AB52" s="31"/>
       <c r="AC52" s="12"/>
       <c r="AD52" s="12"/>
       <c r="AE52" s="12"/>
-      <c r="AF52" s="42"/>
+      <c r="AF52" s="38"/>
       <c r="AG52" s="12"/>
       <c r="AH52" s="12"/>
-      <c r="AI52" s="43"/>
+      <c r="AI52" s="34"/>
       <c r="AJ52" s="12"/>
       <c r="AK52" s="5">
         <f t="shared" si="4"/>
@@ -4333,36 +4333,36 @@
       <c r="E53" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="43"/>
+      <c r="F53" s="34"/>
       <c r="G53" s="31"/>
       <c r="H53" s="31"/>
       <c r="I53" s="31"/>
       <c r="J53" s="31"/>
-      <c r="K53" s="42"/>
+      <c r="K53" s="38"/>
       <c r="L53" s="31"/>
-      <c r="M53" s="43"/>
+      <c r="M53" s="34"/>
       <c r="N53" s="31"/>
       <c r="O53" s="31"/>
       <c r="P53" s="31"/>
       <c r="Q53" s="31"/>
-      <c r="R53" s="42"/>
+      <c r="R53" s="38"/>
       <c r="S53" s="31"/>
-      <c r="T53" s="43"/>
+      <c r="T53" s="34"/>
       <c r="U53" s="31"/>
       <c r="V53" s="31"/>
       <c r="W53" s="31"/>
       <c r="X53" s="31"/>
-      <c r="Y53" s="42"/>
+      <c r="Y53" s="38"/>
       <c r="Z53" s="31"/>
-      <c r="AA53" s="43"/>
+      <c r="AA53" s="34"/>
       <c r="AB53" s="31"/>
       <c r="AC53" s="12"/>
       <c r="AD53" s="12"/>
       <c r="AE53" s="12"/>
-      <c r="AF53" s="42"/>
+      <c r="AF53" s="38"/>
       <c r="AG53" s="12"/>
       <c r="AH53" s="12"/>
-      <c r="AI53" s="43"/>
+      <c r="AI53" s="34"/>
       <c r="AJ53" s="12"/>
       <c r="AK53" s="5">
         <f t="shared" ref="AK53" si="6">COUNTIF(F53:AJ53,"P")</f>
@@ -4375,13 +4375,7 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="A2:AJ2"/>
-    <mergeCell ref="A1:AJ1"/>
-    <mergeCell ref="K5:K53"/>
-    <mergeCell ref="R5:R53"/>
-    <mergeCell ref="Y5:Y53"/>
-    <mergeCell ref="AF5:AF53"/>
+    <mergeCell ref="AM16:AP16"/>
     <mergeCell ref="AL3:AL4"/>
     <mergeCell ref="AM3:AN3"/>
     <mergeCell ref="AM8:AP8"/>
@@ -4390,24 +4384,30 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="AM16:AP16"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="A2:AJ2"/>
+    <mergeCell ref="A1:AJ1"/>
+    <mergeCell ref="K5:K53"/>
+    <mergeCell ref="R5:R53"/>
+    <mergeCell ref="Y5:Y53"/>
+    <mergeCell ref="AF5:AF53"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5 M5 T5 G5:J50 N5:Q50 U5:X50 AB6:AE51 AC52:AE53 AJ5:AJ53 F4:AJ4 L5:L50 K5 S5:S50 R5 Z5:Z50 Y5 AG6:AH53 AA5:AI5">
+  <conditionalFormatting sqref="F5 K5 M5 R5 T5 Y5 AA5:AI5 G5:J50 L5:L50 N5:Q50 S5:S50 U5:X50 Z5:Z50 AJ5:AJ53 AB6:AE51 AG6:AH53 AC52:AE53 F4:AJ4">
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5 M5 T5 G5:J50 N5:Q50 U5:X50 AB6:AE51 AC52:AE53 AJ5:AJ53 L5:L50 K5 S5:S50 R5 Z5:Z50 Y5 AG6:AH53 AA5:AI5">
+  <conditionalFormatting sqref="F5 K5 M5 R5 T5 Y5 AA5:AI5 G5:J50 L5:L50 N5:Q50 S5:S50 U5:X50 Z5:Z50 AJ5:AJ53 AB6:AE51 AG6:AH53 AC52:AE53">
     <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5 M5 T5 G5:J50 N5:Q50 U5:X50 AB6:AE51 AM4:AN4 AC52:AE53 AJ5:AJ53 F3:AJ4 L5:L50 K5 S5:S50 R5 Z5:Z50 Y5 AG6:AH53 AA5:AI5">
+  <conditionalFormatting sqref="F3:AJ4 F5 K5 M5 R5 T5 Y5 AA5:AI5 G5:J50 L5:L50 N5:Q50 S5:S50 U5:X50 Z5:Z50 AJ5:AJ53 AB6:AE51 AG6:AH53 AC52:AE53 AM4:AN4">
     <cfRule type="expression" dxfId="7" priority="16">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:J53 N6:Q53 U6:X53 AB6:AE53 AJ6:AJ53 L6:L53 S6:S53 Z6:Z53 AG6:AH53 F5:AJ5">
+  <conditionalFormatting sqref="F5:AJ5 G6:J53 L6:L53 N6:Q53 S6:S53 U6:X53 Z6:Z53 AB6:AE53 AG6:AH53 AJ6:AJ53">
     <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"A"</formula>
     </cfRule>
